--- a/data/trans_camb/IP16B08-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16B08-Estudios-trans_camb.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,88</t>
+          <t>0,0; 78,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 160,81</t>
+          <t>0,0; 372,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,95</t>
+          <t>0,0; 22,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,57</t>
+          <t>0,0; 22,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,89</t>
+          <t>0,0; 19,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,89</t>
+          <t>0,0; 22,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,02</t>
+          <t>0,0; 15,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,28</t>
+          <t>0,0; 16,17</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,58</t>
+          <t>0,0; 28,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,23</t>
+          <t>0,0; 28,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,48</t>
+          <t>0,0; 24,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,18</t>
+          <t>0,0; 29,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,97</t>
+          <t>0,0; 18,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,43</t>
+          <t>0,0; 19,29</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-62,16; 0,0</t>
+          <t>-66,57; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-49,61; 0,0</t>
+          <t>-42,97; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-62,16; 0,0</t>
+          <t>-66,57; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-49,61; 0,0</t>
+          <t>-42,97; 0,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,68</t>
+          <t>0,0; 20,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,69</t>
+          <t>0,0; 20,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,88; 6,91</t>
+          <t>-20,88; 6,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,4</t>
+          <t>0,0; 17,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 8,72</t>
+          <t>-6,86; 9,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 13,05</t>
+          <t>1,51; 12,32</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,08</t>
+          <t>0,0; 26,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,09</t>
+          <t>0,0; 26,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 7,42</t>
+          <t>-21,3; 7,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,61</t>
+          <t>0,0; 20,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 9,68</t>
+          <t>-6,97; 10,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,54; 15,0</t>
+          <t>1,53; 14,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B08-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16B08-Estudios-trans_camb.xlsx
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,01</t>
+          <t>0,0; 22,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,23</t>
+          <t>0,0; 22,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,75</t>
+          <t>0,0; 22,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,66</t>
+          <t>0,0; 19,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,32</t>
+          <t>0,0; 15,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,17</t>
+          <t>0,0; 14,78</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,23</t>
+          <t>0,0; 28,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,68</t>
+          <t>0,0; 29,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,67</t>
+          <t>0,0; 28,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,29</t>
+          <t>0,0; 24,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,09</t>
+          <t>0,0; 18,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,29</t>
+          <t>0,0; 17,33</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-66,57; 0,0</t>
+          <t>-70,98; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-42,97; 0,0</t>
+          <t>-49,22; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-66,57; 0,0</t>
+          <t>-70,98; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-42,97; 0,0</t>
+          <t>-49,22; 0,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,89</t>
+          <t>0,0; 20,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,74</t>
+          <t>0,0; 20,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,88; 6,95</t>
+          <t>-19,6; 6,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,28</t>
+          <t>0,0; 17,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 9,44</t>
+          <t>-6,8; 9,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 12,32</t>
+          <t>1,48; 12,48</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,4</t>
+          <t>0,0; 25,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,17</t>
+          <t>0,0; 25,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-21,3; 7,45</t>
+          <t>-20,91; 7,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,89</t>
+          <t>0,0; 20,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 10,49</t>
+          <t>-6,94; 10,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,53; 14,04</t>
+          <t>1,5; 14,25</t>
         </is>
       </c>
     </row>
